--- a/work/스페이스X_테슬라_기업분석.xlsx
+++ b/work/스페이스X_테슬라_기업분석.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SPCX $145.23 · TSLA $404.22 (2026-10-28 종가)</t>
+          <t>SPCX $141.71 · TSLA $401.47 (2026-10-29 종가)</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>주가는 2026-10-28 종가. 시가총액과 배수는 수식입니다.</t>
+          <t>주가는 2026-10-29 종가. 시가총액과 배수는 수식입니다.</t>
         </is>
       </c>
     </row>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>145.2299957275391</v>
+        <v>141.7122039794922</v>
       </c>
       <c r="C3" s="19" t="n">
-        <v>404.2200012207031</v>
+        <v>401.4700012207031</v>
       </c>
     </row>
     <row r="4">
@@ -2092,11 +2092,11 @@
       </c>
       <c r="B5" s="8">
         <f>B3*B4</f>
-        <v>1972078111984.2534</v>
+        <v>1924310017837.5244</v>
       </c>
       <c r="C5" s="8">
         <f>C3*C4</f>
-        <v>1597783821757.264</v>
+        <v>1586913737405.764</v>
       </c>
     </row>
     <row r="6">
@@ -2120,11 +2120,11 @@
       </c>
       <c r="B7" s="10">
         <f>B5/B6</f>
-        <v>2655.6397952925577</v>
+        <v>2591.314325124595</v>
       </c>
       <c r="C7" s="10">
         <f>C5/C6</f>
-        <v>502.31351540619784</v>
+        <v>498.8961630654045</v>
       </c>
     </row>
     <row r="8">
@@ -2135,11 +2135,11 @@
       </c>
       <c r="B8" s="8">
         <f>B5*0.1</f>
-        <v>197207811198.42535</v>
+        <v>192431001783.75244</v>
       </c>
       <c r="C8" s="8">
         <f>C5*0.1</f>
-        <v>159778382175.7264</v>
+        <v>158691373740.5764</v>
       </c>
     </row>
     <row r="9">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="B9" s="10">
         <f>B8/B6</f>
-        <v>265.5639795292558</v>
+        <v>259.1314325124595</v>
       </c>
       <c r="C9" s="10">
         <f>C8/C6</f>
-        <v>50.231351540619784</v>
+        <v>49.88961630654045</v>
       </c>
     </row>
   </sheetData>
